--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,48 +1004,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68053819</v>
+        <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>88540</v>
+        <v>91516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3483</v>
+        <v>2008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rutbläcksvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coprinopsis picacea</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Balsberget, Sk</t>
+          <t>Balsberget, 100 m NO om parkeringen, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449439</v>
+        <v>449513</v>
       </c>
       <c r="R5" t="n">
-        <v>6218011</v>
+        <v>6218169</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-10-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-10-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,33 +1094,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>granskog, produktionsskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Tony Svensson, Nils Otto Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68053819</t>
+          <t>https://artportalen.se/Sighting/136777453</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136257279</v>
+        <v>68053819</v>
       </c>
       <c r="B6" t="n">
-        <v>75447</v>
+        <v>88540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,37 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6427</v>
+        <v>3483</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Glansfläck</t>
+          <t>Rutbläcksvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Diarthonis spadicea</t>
+          <t>Coprinopsis picacea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Leight.) Frisch &amp; al.</t>
+          <t>(Bull.:Fr.) Redhead, Vilgalys &amp; Moncalvo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gamlegård NO, Sk</t>
+          <t>Balsberget, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449479</v>
+        <v>449439</v>
       </c>
       <c r="R6" t="n">
-        <v>6218244</v>
+        <v>6218011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1188,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2017-10-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2017-10-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,23 +1202,128 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Ingvarsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68053819</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136257279</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75449</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6427</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Glansfläck</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Diarthonis spadicea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gamlegård NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>449479</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6218244</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fjälkestad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136257279</t>
         </is>
@@ -1217,6 +1336,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91518</v>
+        <v>91520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91520</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91523</v>
+        <v>91529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91529</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91535</v>
+        <v>91548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91548</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91567</v>
+        <v>91569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1415-2024 artfynd.xlsx
+++ b/artfynd/A 1415-2024 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>136777453</v>
       </c>
       <c r="B5" t="n">
-        <v>91569</v>
+        <v>91574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
